--- a/pohlavi.xlsx
+++ b/pohlavi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programování\python\projekt_urazy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\python\projekt_urazy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B235025-0984-448C-8CE2-4C480C19142C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81800B50-48BC-4BF3-99BB-4ED066FD19DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{07D856A2-C59F-4990-8D1B-94BA692740FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{07D856A2-C59F-4990-8D1B-94BA692740FA}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>2010</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>rok</t>
   </si>
 </sst>
 </file>
@@ -139,7 +142,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normální" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -155,7 +158,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -452,141 +455,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0927F048-63CD-4FD9-A543-31572555207E}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B3" s="2">
         <v>28574.606983169593</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C3" s="2">
         <v>27596.588739116862</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D3" s="2">
         <v>27559.059234765115</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E3" s="2">
         <v>27644.245483672257</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F3" s="2">
         <v>28216.893921818868</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G3" s="2">
         <v>28860.812944799112</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H3" s="2">
         <v>29126.094302541183</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I3" s="2">
         <v>28822.245948161522</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J3" s="2">
         <v>28742.510288520985</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K3" s="2">
         <v>28388.678595355537</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L3" s="2">
         <v>24464.015205011165</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M3" s="2">
         <v>25663.536708286916</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N3" s="2">
         <v>27812.651466330652</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B4" s="2">
         <v>22012.945260144024</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C4" s="2">
         <v>21152.614388557824</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="2">
         <v>21334.43178488786</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E4" s="2">
         <v>21769.859995413117</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F4" s="2">
         <v>22270.443925669439</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G4" s="2">
         <v>23263.287857896197</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H4" s="2">
         <v>23883.046402905988</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I4" s="2">
         <v>24038.377341072719</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J4" s="2">
         <v>24070.326250192855</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K4" s="2">
         <v>24112.628996653046</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L4" s="2">
         <v>20789.271660689403</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M4" s="2">
         <v>21901.910618774062</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N4" s="2">
         <v>23476.057101586772</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
